--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/TENNESSEE_2020.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2020/TENNESSEE_2020.xlsx
@@ -2058,7 +2058,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Guerero</t>
+          <t>Guerrero</t>
         </is>
       </c>
       <c r="C95">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C165">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C238">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="B248" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C248">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Tixtla De Guerero</t>
+          <t>Tixtla De Guerrero</t>
         </is>
       </c>
       <c r="C327">
@@ -7080,7 +7080,7 @@
       </c>
       <c r="B374" t="inlineStr">
         <is>
-          <t>Santiago Tulantepec De Lugo Guerero</t>
+          <t>Santiago Tulantepec De Lugo Guerrero</t>
         </is>
       </c>
       <c r="C374">
@@ -7188,7 +7188,7 @@
       </c>
       <c r="B380" t="inlineStr">
         <is>
-          <t>Tepehuacan De Guerero</t>
+          <t>Tepehuacan De Guerrero</t>
         </is>
       </c>
       <c r="C380">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Villa Guerero</t>
+          <t>Villa Guerrero</t>
         </is>
       </c>
       <c r="C443">
@@ -10698,7 +10698,7 @@
       </c>
       <c r="B575" t="inlineStr">
         <is>
-          <t>Cuilapam De Guerero</t>
+          <t>Cuilapam De Guerrero</t>
         </is>
       </c>
       <c r="C575">
@@ -10986,7 +10986,7 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Putla Villa De Guerero</t>
+          <t>Putla Villa De Guerrero</t>
         </is>
       </c>
       <c r="C591">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="B626" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C626">
@@ -11976,7 +11976,7 @@
       </c>
       <c r="B646" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C646">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="B649" t="inlineStr">
         <is>
-          <t>San Pedro Totolapa</t>
+          <t>San Pedro Totolapam</t>
         </is>
       </c>
       <c r="C649">
@@ -14118,7 +14118,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>Vicente Guerero</t>
+          <t>Vicente Guerrero</t>
         </is>
       </c>
       <c r="C765">
@@ -16548,7 +16548,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>Ziltlaltepec De Trinidad Sanchez Santos</t>
+          <t>Zitlaltepec De Trinidad Sanchez Santos</t>
         </is>
       </c>
       <c r="C900">
